--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487676_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487676_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. SISTAC RODRIGUEZ</t>
+          <t>J. GALLETTO LAMELA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5991</v>
+        <v>6.1842</v>
       </c>
       <c r="E2" t="n">
-        <v>4.737</v>
+        <v>5.334</v>
       </c>
       <c r="F2" t="n">
-        <v>0.862</v>
+        <v>0.8502</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3282</v>
+        <v>5.5627</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0175</v>
+        <v>-1.4088</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3108</v>
+        <v>6.9715</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0448</v>
+        <v>6.406</v>
       </c>
       <c r="K2" t="n">
-        <v>2.7229</v>
+        <v>0.0907</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3219</v>
+        <v>6.3153</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.7166</v>
+        <v>-0.8433</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.7054</v>
+        <v>-1.4995</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0111</v>
+        <v>0.6562</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7463</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7164</v>
+        <v>2.1344</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0292</v>
+        <v>0.5036</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4385</v>
+        <v>0.0504</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4677</v>
+        <v>0.4531</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5537</v>
+        <v>0.894</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2239</v>
+        <v>1.788</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3299</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. GALLETTO LAMELA</t>
+          <t>A. SISTAC RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4507</v>
+        <v>5.6681</v>
       </c>
       <c r="E3" t="n">
-        <v>4.873</v>
+        <v>4.3972</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5777</v>
+        <v>1.2709</v>
       </c>
       <c r="G3" t="n">
-        <v>5.5627</v>
+        <v>2.3282</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.4088</v>
+        <v>1.0175</v>
       </c>
       <c r="I3" t="n">
-        <v>6.9715</v>
+        <v>1.3108</v>
       </c>
       <c r="J3" t="n">
-        <v>6.406</v>
+        <v>4.0448</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0907</v>
+        <v>2.7229</v>
       </c>
       <c r="L3" t="n">
-        <v>6.3153</v>
+        <v>1.3219</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8433</v>
+        <v>-1.7166</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4995</v>
+        <v>-1.7054</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6562</v>
+        <v>-0.0111</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7761</v>
+        <v>1.7463</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1344</v>
+        <v>2.7164</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2299</v>
+        <v>0.0398</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4105</v>
+        <v>0.0987</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1806</v>
+        <v>-0.0589</v>
       </c>
       <c r="V3" t="n">
-        <v>0.894</v>
+        <v>1.5537</v>
       </c>
       <c r="W3" t="n">
-        <v>1.788</v>
+        <v>1.2239</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.894</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. NIMAGA</t>
+          <t>E. DUQUE NEGRÍN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5261</v>
+        <v>3.2572</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5561</v>
+        <v>1.5162</v>
       </c>
       <c r="F4" t="n">
-        <v>2.97</v>
+        <v>1.741</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7413999999999999</v>
+        <v>1.2754</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4161</v>
+        <v>-0.0643</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3253</v>
+        <v>1.3397</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0887</v>
+        <v>0.6889</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8857</v>
+        <v>0.6838</v>
       </c>
       <c r="L4" t="n">
-        <v>0.203</v>
+        <v>0.005</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3473</v>
+        <v>0.5866</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4696</v>
+        <v>-0.7481</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1223</v>
+        <v>1.3347</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3881</v>
+        <v>0.7761</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9105</v>
+        <v>-1.1642</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5224</v>
+        <v>1.9403</v>
       </c>
       <c r="S4" t="n">
-        <v>2.843</v>
+        <v>-0.0182</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1541</v>
+        <v>-0.4562</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6889</v>
+        <v>0.438</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3299</v>
+        <v>1.2239</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2239</v>
+        <v>2.4477</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.894</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. DUQUE NEGRÍN</t>
+          <t>M. NIMAGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3358</v>
+        <v>1.7408</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8946</v>
+        <v>-0.3843</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4412</v>
+        <v>2.1251</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2754</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0643</v>
+        <v>0.4161</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3397</v>
+        <v>0.3253</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6889</v>
+        <v>1.0887</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6838</v>
+        <v>0.8857</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005</v>
+        <v>0.203</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5866</v>
+        <v>-0.3473</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7481</v>
+        <v>-0.4696</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3347</v>
+        <v>0.1223</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7761</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1642</v>
+        <v>-2.9105</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9403</v>
+        <v>2.5224</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9397</v>
+        <v>1.0577</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0779</v>
+        <v>0.2136</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1382</v>
+        <v>0.844</v>
       </c>
       <c r="V5" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.2239</v>
       </c>
-      <c r="W5" t="n">
-        <v>2.4477</v>
-      </c>
       <c r="X5" t="n">
-        <v>-1.2239</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1428</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.9889</v>
+        <v>-2.089</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1317</v>
+        <v>2.1862</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6469</v>
@@ -922,13 +922,13 @@
         <v>1.1642</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4121</v>
+        <v>0.3665</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2434</v>
+        <v>0.1433</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1687</v>
+        <v>0.2232</v>
       </c>
       <c r="V6" t="n">
         <v>0.3776</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.281</v>
+        <v>-0.0837</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6462</v>
+        <v>-1.2854</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3652</v>
+        <v>1.2017</v>
       </c>
       <c r="G7" t="n">
         <v>-1.5704</v>
@@ -1000,13 +1000,13 @@
         <v>2.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3524</v>
+        <v>-0.155</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0173</v>
+        <v>-0.6564</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6649</v>
+        <v>0.5014</v>
       </c>
       <c r="V7" t="n">
         <v>1.8358</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.706</v>
+        <v>-0.5787</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7672</v>
+        <v>-0.6671</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0612</v>
+        <v>0.0885</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9305</v>
@@ -1078,13 +1078,13 @@
         <v>0.3881</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1635</v>
+        <v>-0.0362</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1817</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. FERNANDEZ SHEPHARD</t>
+          <t>K. RIVEROL DE LAS CASAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5335</v>
+        <v>-2.3887</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3712</v>
+        <v>-2.1105</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1623</v>
+        <v>-0.2782</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0323</v>
+        <v>-2.0255</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2463</v>
+        <v>-1.5884</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2786</v>
+        <v>-0.437</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4143</v>
+        <v>-2.0897</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9598</v>
+        <v>-0.5849</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5455</v>
+        <v>-1.5048</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4466</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7135</v>
+        <v>-1.0035</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2669</v>
+        <v>1.0677</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.7463</v>
+        <v>0.3881</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1344</v>
+        <v>-1.1642</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3881</v>
+        <v>1.5523</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5451</v>
+        <v>-0.0805</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6842</v>
+        <v>-0.0589</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.894</v>
+        <v>-0.6119</v>
       </c>
       <c r="W9" t="n">
-        <v>0.894</v>
+        <v>1.2239</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.788</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. RIVEROL DE LAS CASAS</t>
+          <t>B. FERNANDEZ SHEPHARD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6917</v>
+        <v>-2.409</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3317</v>
+        <v>-1.1104</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3599</v>
+        <v>-1.2986</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0255</v>
+        <v>-0.0323</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5884</v>
+        <v>0.2463</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.437</v>
+        <v>-0.2786</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0897</v>
+        <v>0.4143</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5849</v>
+        <v>0.9598</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.5048</v>
+        <v>-0.5455</v>
       </c>
       <c r="M10" t="n">
-        <v>0.06419999999999999</v>
+        <v>-0.4466</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0035</v>
+        <v>-0.7135</v>
       </c>
       <c r="O10" t="n">
-        <v>1.0677</v>
+        <v>0.2669</v>
       </c>
       <c r="P10" t="n">
+        <v>-1.7463</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-2.1344</v>
+      </c>
+      <c r="R10" t="n">
         <v>0.3881</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-1.1642</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.5523</v>
-      </c>
       <c r="S10" t="n">
-        <v>-0.4424</v>
+        <v>0.2636</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3017</v>
+        <v>-0.2843</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1406</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6119</v>
+        <v>-0.894</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2239</v>
+        <v>0.894</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8358</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0077</v>
+        <v>-4.0473</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3187</v>
+        <v>-3.3582</v>
       </c>
       <c r="F11" t="n">
         <v>-0.6889999999999999</v>
@@ -1312,10 +1312,10 @@
         <v>0.7761</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4004</v>
+        <v>0.3609</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1951</v>
+        <v>0.1556</v>
       </c>
       <c r="U11" t="n">
         <v>0.2053</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.834600000000002</v>
+        <v>7.440100000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3632000000000017</v>
+        <v>0.2424999999999988</v>
       </c>
       <c r="F12" t="n">
-        <v>7.197800000000001</v>
+        <v>7.197799999999999</v>
       </c>
       <c r="G12" t="n">
         <v>5.000000000000001</v>
@@ -1360,19 +1360,19 @@
         <v>-4.4818</v>
       </c>
       <c r="I12" t="n">
-        <v>9.481999999999999</v>
+        <v>9.481999999999998</v>
       </c>
       <c r="J12" t="n">
-        <v>9.3896</v>
+        <v>9.389600000000002</v>
       </c>
       <c r="K12" t="n">
-        <v>4.5232</v>
+        <v>4.523200000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>4.8663</v>
+        <v>4.866300000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.389599999999999</v>
+        <v>-4.3896</v>
       </c>
       <c r="N12" t="n">
         <v>-9.005099999999999</v>
@@ -1390,13 +1390,13 @@
         <v>16.4928</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6375</v>
+        <v>2.243300000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.5031</v>
+        <v>-0.8974</v>
       </c>
       <c r="U12" t="n">
-        <v>3.1407</v>
+        <v>3.1405</v>
       </c>
       <c r="V12" t="n">
         <v>3.1075</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
+          <t>A. GOMEZ SERRANO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.6043</v>
+        <v>2.228</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8534</v>
+        <v>0.8433</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7509</v>
+        <v>1.3847</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9882</v>
+        <v>-0.6937</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1328</v>
+        <v>-0.0503</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1446</v>
+        <v>-0.6434</v>
       </c>
       <c r="J13" t="n">
-        <v>1.034</v>
+        <v>-0.1695</v>
       </c>
       <c r="K13" t="n">
-        <v>1.034</v>
+        <v>-0.2101</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.0406</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0458</v>
+        <v>-0.5242</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0989</v>
+        <v>0.1598</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1446</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5523</v>
+        <v>1.7463</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.3881</v>
+        <v>-0.194</v>
       </c>
       <c r="R13" t="n">
         <v>1.9403</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9578</v>
+        <v>-0.3306</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2075</v>
+        <v>-0.2992</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7504</v>
+        <v>-0.0314</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.894</v>
+        <v>1.506</v>
       </c>
       <c r="W13" t="n">
+        <v>1.506</v>
+      </c>
+      <c r="X13" t="n">
         <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-0.894</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. GOMEZ SERRANO</t>
+          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8309</v>
+        <v>1.9313</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7432</v>
+        <v>0.453</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0877</v>
+        <v>1.4784</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6937</v>
+        <v>0.9882</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0503</v>
+        <v>1.1328</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6434</v>
+        <v>-0.1446</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1695</v>
+        <v>1.034</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2101</v>
+        <v>1.034</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0406</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5242</v>
+        <v>-0.0458</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1598</v>
+        <v>0.0989</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.1446</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7463</v>
+        <v>1.5523</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.194</v>
+        <v>-0.3881</v>
       </c>
       <c r="R14" t="n">
         <v>1.9403</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7277</v>
+        <v>0.2849</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3993</v>
+        <v>-0.1929</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3284</v>
+        <v>0.4778</v>
       </c>
       <c r="V14" t="n">
-        <v>1.506</v>
+        <v>-0.894</v>
       </c>
       <c r="W14" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3255</v>
+        <v>1.013</v>
       </c>
       <c r="E15" t="n">
-        <v>1.521</v>
+        <v>1.0205</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1955</v>
+        <v>-0.0075</v>
       </c>
       <c r="G15" t="n">
         <v>-1.6735</v>
@@ -1624,13 +1624,13 @@
         <v>2.5224</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1945</v>
+        <v>-0.118</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1233</v>
+        <v>-0.3772</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0711</v>
+        <v>0.2591</v>
       </c>
       <c r="V15" t="n">
         <v>0.2821</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5809</v>
+        <v>0.0709</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.5053</v>
+        <v>-1.205</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9245</v>
+        <v>1.276</v>
       </c>
       <c r="G16" t="n">
         <v>0.906</v>
@@ -1702,13 +1702,13 @@
         <v>1.7463</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0794</v>
+        <v>-0.4276</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7874</v>
+        <v>-0.4871</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.292</v>
+        <v>0.0595</v>
       </c>
       <c r="V16" t="n">
         <v>-0.9896</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SANCHEZ SANCHEZ</t>
+          <t>E. BOADA MONTESDEOCA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.905</v>
+        <v>-0.5334</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.3119</v>
+        <v>0.193</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4069</v>
+        <v>-0.7264</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6986</v>
+        <v>-0.3667</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1022</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8008</v>
+        <v>0.5511</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.2935</v>
+        <v>1.5209</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0412</v>
+        <v>0.2802</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3347</v>
+        <v>1.2407</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5948</v>
+        <v>-1.8875</v>
       </c>
       <c r="N17" t="n">
-        <v>0.061</v>
+        <v>-1.1979</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5339</v>
+        <v>-0.6896</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5821</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1642</v>
+        <v>-3.1045</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5821</v>
+        <v>2.1344</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3757</v>
+        <v>-0.0906</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1458</v>
+        <v>-0.3413</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2299</v>
+        <v>0.2507</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.1179</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. BOADA MONTESDEOCA</t>
+          <t>M. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.188</v>
+        <v>-0.7048</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1073</v>
+        <v>-2.1117</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0807</v>
+        <v>1.4069</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3667</v>
+        <v>-0.6986</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9177999999999999</v>
+        <v>0.1022</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5511</v>
+        <v>-0.8008</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5209</v>
+        <v>-1.2935</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2802</v>
+        <v>0.0412</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2407</v>
+        <v>-1.3347</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8875</v>
+        <v>0.5948</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1979</v>
+        <v>0.061</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6896</v>
+        <v>0.5339</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9702</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1045</v>
+        <v>-1.1642</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1344</v>
+        <v>0.5821</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7452</v>
+        <v>0.5759</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.346</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1036</v>
+        <v>0.2299</v>
       </c>
       <c r="V18" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1179</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7509</v>
+        <v>-1.3538</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2644</v>
+        <v>-1.1643</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4865</v>
+        <v>-0.1895</v>
       </c>
       <c r="G19" t="n">
         <v>0.8836000000000001</v>
@@ -1936,13 +1936,13 @@
         <v>1.3582</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4002</v>
+        <v>-0.0031</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2423</v>
+        <v>-0.1422</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1579</v>
+        <v>0.1391</v>
       </c>
       <c r="V19" t="n">
         <v>-1.4582</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8142</v>
+        <v>-2.3593</v>
       </c>
       <c r="E20" t="n">
         <v>0.0266</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8409</v>
+        <v>-2.386</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2267</v>
@@ -2014,13 +2014,13 @@
         <v>2.3284</v>
       </c>
       <c r="S20" t="n">
-        <v>0.08409999999999999</v>
+        <v>-0.461</v>
       </c>
       <c r="T20" t="n">
         <v>-0.6651</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7493</v>
+        <v>0.2042</v>
       </c>
       <c r="V20" t="n">
         <v>-1.8358</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3095</v>
+        <v>-3.0191</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1965</v>
+        <v>-1.7971</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1131</v>
+        <v>-1.2221</v>
       </c>
       <c r="G21" t="n">
         <v>-1.491</v>
@@ -2092,13 +2092,13 @@
         <v>0.9702</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7158</v>
+        <v>0.0062</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5473</v>
+        <v>-0.0533</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1685</v>
+        <v>0.0595</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5642</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0466</v>
+        <v>-3.4399</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9566</v>
+        <v>-3.4561</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.09</v>
+        <v>0.0162</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6276</v>
@@ -2170,13 +2170,13 @@
         <v>3.8806</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.013</v>
+        <v>-0.4063</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4289</v>
+        <v>-0.9284</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4159</v>
+        <v>0.5221</v>
       </c>
       <c r="V22" t="n">
         <v>-0.0478</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.8344</v>
+        <v>-6.1671</v>
       </c>
       <c r="E23" t="n">
         <v>-7.1978</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3632999999999998</v>
+        <v>1.030700000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-5</v>
@@ -2248,13 +2248,13 @@
         <v>19.4032</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6376</v>
+        <v>-0.9702000000000001</v>
       </c>
       <c r="T23" t="n">
         <v>-3.1407</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5032</v>
+        <v>2.1705</v>
       </c>
       <c r="V23" t="n">
         <v>-3.1075</v>
